--- a/lib/us_core_test_kit/requirements/hl7.fhir.us.core_7.0.0_reqs.xlsx
+++ b/lib/us_core_test_kit/requirements/hl7.fhir.us.core_7.0.0_reqs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/knaden/Documents/Inferno/source/us-core-test-kit/lib/us_core_test_kit/requirements/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/edeyoung/Documents/inferno/us-core-test-kit/lib/us_core_test_kit/requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A134E3-941E-7845-A343-6D07F83D6EF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39E9EDD5-F921-5445-8E9A-D4C802F2486A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20180" activeTab="2" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
+    <workbookView xWindow="20" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{D251129A-65BB-5042-909C-749E11B8C0B0}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="9" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2860" uniqueCount="998">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2858" uniqueCount="1003">
   <si>
     <r>
       <rPr>
@@ -3838,37 +3838,10 @@
     <t>https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-patient.html#mandatory-and-must-support-data-elements, https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html#profile-specific-implementation-guidance</t>
   </si>
   <si>
-    <t>[Organizations participating in the ONC Health IT certrification program,] must support at least one category code from OMB Race [category for the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
-  </si>
-  <si>
-    <t>For organizations participating in ONC certification, when using the US Core Race Extension</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-patient.html#mandatory-and-must-support-data-elements, https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-ethnicity.html#profile-specific-implementation-guidance</t>
   </si>
   <si>
-    <t>[Organizations participating in the ONC Health IT certrification program,] must support at least one category code from OMB … Ethnicity [category for the [US Core Ethnicity Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-ethnicity.html)]</t>
-  </si>
-  <si>
-    <t>For organizations participating in ONC certification, When using the US Core Ethnicity Extension</t>
-  </si>
-  <si>
-    <t>[Organizations participating in the ONC Health IT certrification program,] MAY include additional detailed codes from CDC Race … codes [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
-  </si>
-  <si>
-    <t>For organizations participating in ONC certification, When using the US Core Race Extension</t>
-  </si>
-  <si>
-    <t>[Organizations participating in the ONC Health IT certrification program,] SHALL include a text description [of category codes when using the [US Core Ethnicity Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-ethnicity.html)]</t>
-  </si>
-  <si>
     <t>https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-patient.html#mandatory-and-must-support-data-elements</t>
-  </si>
-  <si>
-    <t>[For Organizations participating in the ONC Health IT certrification program,] Although Patient.deceased[x] is marked as additional USCDI, certifying systems are not required to support both [boolean and dateTime data types], but SHALL support [at] least Patient.deceasedDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">For organizations participating in ONC certification, </t>
   </si>
   <si>
     <t>Proposal for a potentially better way to state this requirement: Certified system SHALL support Patient.deceasedDateTime and MAY support Patient.deceasedBoolean. Non certified system SHALL support at least one date type under Patient.deceased[x]</t>
@@ -4581,6 +4554,48 @@
   </si>
   <si>
     <t>OUT OF SCOPE</t>
+  </si>
+  <si>
+    <t>Marked DEPRECATED because this is an example.</t>
+  </si>
+  <si>
+    <t>Duplicate of 254</t>
+  </si>
+  <si>
+    <t>Duplicate of requirement 260</t>
+  </si>
+  <si>
+    <t>Although Patient.deceased[x] is marked as additional USCDI, certifying systems are not required to support both [boolean and dateTime data types], but SHALL support [at] least Patient.deceasedDateTime</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for Race ... allow[s] for one or more codes of which must support at least one category code from OMB Race [category for the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for Race ... allow[s] for one or more codes of which MAY include additional detailed codes from CDC Race … codes [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for Race ... allow[s] for one or more codes of which SHALL include a text description [of category codes when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for ... Ethnicity allow[s] for one or more codes of which must support at least one category code from OMB … Ethnicity [category for the [US Core Ethnicity Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-ethnicity.html)]</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for ... Ethnicity allow[s] for one or more codes of which MAY include additional detailed codes from CDC Race … codes [when using the [US Core Race Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-race.html)]</t>
+  </si>
+  <si>
+    <t>The Complex [Extension] for ... Ethnicity allow[s] for one or more codes of which SHALL include a text description [of category codes when using the [US Core Ethnicity Extension] (https://hl7.org/fhir/us/core/STU7/StructureDefinition-us-core-ethnicity.html)]</t>
+  </si>
+  <si>
+    <t>when using the US Core Race Extension</t>
+  </si>
+  <si>
+    <t>When using the US Core Ethnicity Extension</t>
+  </si>
+  <si>
+    <t>When using the US Core Race Extension</t>
+  </si>
+  <si>
+    <t>certifying systems</t>
   </si>
 </sst>
 </file>
@@ -9185,7 +9200,7 @@
         <v>87</v>
       </c>
       <c r="B88" s="7" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="C88" s="8" t="s">
         <v>182</v>
@@ -9205,7 +9220,7 @@
       </c>
       <c r="N88" s="9" t="str" cm="1">
         <f t="array" ref="N88">SECTION_NAME(B88)</f>
-        <v>additional-uscdi-requirements</v>
+        <v>defined-pattern-elements</v>
       </c>
       <c r="O88" s="10" t="str">
         <f t="shared" si="4"/>
@@ -9230,7 +9245,7 @@
         <v>185</v>
       </c>
       <c r="D89" s="7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E89" s="7" t="s">
         <v>33</v>
@@ -9257,6 +9272,9 @@
         <f t="shared" si="3"/>
         <v>Server</v>
       </c>
+      <c r="V89" s="12" t="s">
+        <v>989</v>
+      </c>
     </row>
     <row r="90" spans="1:22" ht="136" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
@@ -9269,7 +9287,7 @@
         <v>187</v>
       </c>
       <c r="D90" s="7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>76</v>
@@ -9295,6 +9313,9 @@
       <c r="P90" s="10" t="str">
         <f t="shared" si="3"/>
         <v>Client</v>
+      </c>
+      <c r="V90" s="12" t="s">
+        <v>989</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="68" x14ac:dyDescent="0.2">
@@ -15150,7 +15171,7 @@
         <v>support-requirements</v>
       </c>
     </row>
-    <row r="241" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A241" s="7">
         <v>240</v>
       </c>
@@ -15181,7 +15202,7 @@
         <v>support-requirements</v>
       </c>
     </row>
-    <row r="242" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A242" s="7">
         <v>241</v>
       </c>
@@ -15212,7 +15233,7 @@
         <v>support-requirements</v>
       </c>
     </row>
-    <row r="243" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A243" s="7">
         <v>242</v>
       </c>
@@ -15243,7 +15264,7 @@
         <v>discovering-server-read-and-write-formats</v>
       </c>
     </row>
-    <row r="244" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A244" s="7">
         <v>243</v>
       </c>
@@ -15274,7 +15295,7 @@
         <v>discovering-server-read-and-write-formats</v>
       </c>
     </row>
-    <row r="245" spans="1:17" ht="187" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A245" s="7">
         <v>244</v>
       </c>
@@ -15305,7 +15326,7 @@
         <v>discovering-server-read-and-write-formats</v>
       </c>
     </row>
-    <row r="246" spans="1:17" ht="187" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A246" s="7">
         <v>245</v>
       </c>
@@ -15336,7 +15357,7 @@
         <v>discovering-server-read-and-write-formats</v>
       </c>
     </row>
-    <row r="247" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A247" s="7">
         <v>246</v>
       </c>
@@ -15375,7 +15396,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="248" spans="1:17" ht="119" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:22" ht="119" x14ac:dyDescent="0.2">
       <c r="A248" s="7">
         <v>247</v>
       </c>
@@ -15417,7 +15438,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="249" spans="1:17" ht="85" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A249" s="7">
         <v>248</v>
       </c>
@@ -15456,7 +15477,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="250" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A250" s="7">
         <v>249</v>
       </c>
@@ -15498,7 +15519,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="251" spans="1:17" ht="68" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:22" ht="68" x14ac:dyDescent="0.2">
       <c r="A251" s="7">
         <v>250</v>
       </c>
@@ -15540,7 +15561,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="252" spans="1:17" ht="102" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A252" s="7">
         <v>251</v>
       </c>
@@ -15582,7 +15603,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="253" spans="1:17" ht="204" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:22" ht="204" x14ac:dyDescent="0.2">
       <c r="A253" s="7">
         <v>252</v>
       </c>
@@ -15621,7 +15642,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="254" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A254" s="7">
         <v>253</v>
       </c>
@@ -15660,7 +15681,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="255" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A255" s="7">
         <v>254</v>
       </c>
@@ -15699,7 +15720,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="256" spans="1:17" ht="170" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:22" ht="170" x14ac:dyDescent="0.2">
       <c r="A256" s="7">
         <v>255</v>
       </c>
@@ -15710,7 +15731,7 @@
         <v>488</v>
       </c>
       <c r="D256" s="7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>33</v>
@@ -15737,6 +15758,9 @@
       <c r="Q256" s="10" t="s">
         <v>489</v>
       </c>
+      <c r="V256" s="12" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="257" spans="1:22" ht="238" x14ac:dyDescent="0.2">
       <c r="A257" s="7">
@@ -15908,7 +15932,7 @@
         <v>33</v>
       </c>
       <c r="G261" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M261" s="9" t="str" cm="1">
         <f t="array" ref="M261">PAGE_NAME(B261)</f>
@@ -15941,7 +15965,7 @@
         <v>496</v>
       </c>
       <c r="D262" s="7" t="s">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>33</v>
@@ -15968,6 +15992,9 @@
       <c r="Q262" s="10" t="s">
         <v>497</v>
       </c>
+      <c r="V262" s="12" t="s">
+        <v>991</v>
+      </c>
     </row>
     <row r="263" spans="1:22" ht="187" x14ac:dyDescent="0.2">
       <c r="A263" s="7">
@@ -22998,7 +23025,7 @@
         <v/>
       </c>
     </row>
-    <row r="449" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A449" s="7">
         <v>448</v>
       </c>
@@ -23034,7 +23061,7 @@
         <v/>
       </c>
     </row>
-    <row r="450" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+    <row r="450" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A450" s="7">
         <v>449</v>
       </c>
@@ -23073,7 +23100,7 @@
         <v/>
       </c>
     </row>
-    <row r="451" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A451" s="7">
         <v>450</v>
       </c>
@@ -23112,7 +23139,7 @@
         <v/>
       </c>
     </row>
-    <row r="452" spans="1:22" ht="102" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A452" s="7">
         <v>451</v>
       </c>
@@ -23151,7 +23178,7 @@
         <v>Server</v>
       </c>
     </row>
-    <row r="453" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A453" s="7">
         <v>452</v>
       </c>
@@ -23190,7 +23217,7 @@
         <v/>
       </c>
     </row>
-    <row r="454" spans="1:22" ht="68" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:16" ht="68" x14ac:dyDescent="0.2">
       <c r="A454" s="7">
         <v>453</v>
       </c>
@@ -23229,7 +23256,7 @@
         <v/>
       </c>
     </row>
-    <row r="455" spans="1:22" ht="136" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:16" ht="136" x14ac:dyDescent="0.2">
       <c r="A455" s="7">
         <v>454</v>
       </c>
@@ -23268,7 +23295,7 @@
         <v/>
       </c>
     </row>
-    <row r="456" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A456" s="7">
         <v>455</v>
       </c>
@@ -23304,7 +23331,7 @@
         <v/>
       </c>
     </row>
-    <row r="457" spans="1:22" ht="51" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A457" s="7">
         <v>456</v>
       </c>
@@ -23340,7 +23367,7 @@
         <v/>
       </c>
     </row>
-    <row r="458" spans="1:22" ht="34" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A458" s="7">
         <v>457</v>
       </c>
@@ -23376,7 +23403,7 @@
         <v/>
       </c>
     </row>
-    <row r="459" spans="1:22" ht="102" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:16" ht="102" x14ac:dyDescent="0.2">
       <c r="A459" s="7">
         <v>458</v>
       </c>
@@ -23412,7 +23439,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A460" s="7">
         <v>459</v>
       </c>
@@ -23420,7 +23447,7 @@
         <v>819</v>
       </c>
       <c r="C460" s="8" t="s">
-        <v>820</v>
+        <v>993</v>
       </c>
       <c r="D460" s="7" t="s">
         <v>32</v>
@@ -23432,7 +23459,7 @@
         <v>1</v>
       </c>
       <c r="H460" s="12" t="s">
-        <v>821</v>
+        <v>999</v>
       </c>
       <c r="M460" s="9" t="str" cm="1">
         <f t="array" ref="M460">PAGE_NAME(B460)</f>
@@ -23450,19 +23477,16 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="V460" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="461" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="461" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A461" s="7">
         <v>460</v>
       </c>
       <c r="B461" s="52" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C461" s="8" t="s">
-        <v>823</v>
+        <v>996</v>
       </c>
       <c r="D461" s="7" t="s">
         <v>32</v>
@@ -23474,7 +23498,7 @@
         <v>1</v>
       </c>
       <c r="H461" s="12" t="s">
-        <v>824</v>
+        <v>1000</v>
       </c>
       <c r="M461" s="9" t="str" cm="1">
         <f t="array" ref="M461">PAGE_NAME(B461)</f>
@@ -23492,11 +23516,8 @@
         <f>IF(ISNUMBER( SEARCH("server",#REF!)), "Server", IF(ISNUMBER( SEARCH("Server",#REF!)), "Server", IF(ISNUMBER( SEARCH("client",#REF!)), "Client", IF(ISNUMBER( SEARCH("Client",#REF!)), "Client", IF(ISNUMBER( SEARCH("US Core Responder",#REF!)), "Server", IF(ISNUMBER( SEARCH("US Core Requestor",#REF!)), "Client", ""))))))</f>
         <v/>
       </c>
-      <c r="V461" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="462" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="462" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A462" s="7">
         <v>461</v>
       </c>
@@ -23504,7 +23525,7 @@
         <v>819</v>
       </c>
       <c r="C462" s="8" t="s">
-        <v>825</v>
+        <v>994</v>
       </c>
       <c r="D462" s="7" t="s">
         <v>40</v>
@@ -23516,7 +23537,7 @@
         <v>1</v>
       </c>
       <c r="H462" s="12" t="s">
-        <v>826</v>
+        <v>1001</v>
       </c>
       <c r="M462" s="9" t="str" cm="1">
         <f t="array" ref="M462">PAGE_NAME(B462)</f>
@@ -23534,19 +23555,16 @@
         <f>IF(ISNUMBER(SEARCH("server", C461)), "Server", IF(ISNUMBER(SEARCH("Server", C461)), "Server", IF(ISNUMBER(SEARCH("client", C461)), "Client", IF(ISNUMBER(SEARCH("Client", C461)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C461)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C461)), "Client", ""))))))</f>
         <v/>
       </c>
-      <c r="V462" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="463" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="463" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A463" s="7">
         <v>462</v>
       </c>
       <c r="B463" s="52" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C463" s="8" t="s">
-        <v>827</v>
+        <v>995</v>
       </c>
       <c r="D463" s="7" t="s">
         <v>40</v>
@@ -23558,7 +23576,7 @@
         <v>1</v>
       </c>
       <c r="H463" s="12" t="s">
-        <v>824</v>
+        <v>1000</v>
       </c>
       <c r="M463" s="9" t="str" cm="1">
         <f t="array" ref="M463">PAGE_NAME(B463)</f>
@@ -23576,11 +23594,8 @@
         <f t="shared" ref="P463:P494" si="20">IF(ISNUMBER(SEARCH("server", C463)), "Server", IF(ISNUMBER(SEARCH("Server", C463)), "Server", IF(ISNUMBER(SEARCH("client", C463)), "Client", IF(ISNUMBER(SEARCH("Client", C463)), "Client", IF(ISNUMBER(SEARCH("US Core Responder", C463)), "Server", IF(ISNUMBER(SEARCH("US Core Requestor", C463)), "Client", ""))))))</f>
         <v/>
       </c>
-      <c r="V463" s="12" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="464" spans="1:22" ht="85" x14ac:dyDescent="0.2">
+    </row>
+    <row r="464" spans="1:16" ht="85" x14ac:dyDescent="0.2">
       <c r="A464" s="7">
         <v>463</v>
       </c>
@@ -23588,7 +23603,7 @@
         <v>819</v>
       </c>
       <c r="C464" s="8" t="s">
-        <v>825</v>
+        <v>997</v>
       </c>
       <c r="D464" s="7" t="s">
         <v>32</v>
@@ -23600,7 +23615,7 @@
         <v>1</v>
       </c>
       <c r="H464" s="12" t="s">
-        <v>826</v>
+        <v>1001</v>
       </c>
       <c r="M464" s="9" t="str" cm="1">
         <f t="array" ref="M464">PAGE_NAME(B464)</f>
@@ -23618,19 +23633,16 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V464" s="12" t="s">
-        <v>700</v>
-      </c>
     </row>
     <row r="465" spans="1:22" ht="85" x14ac:dyDescent="0.2">
       <c r="A465" s="7">
         <v>464</v>
       </c>
       <c r="B465" s="52" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C465" s="8" t="s">
-        <v>827</v>
+        <v>998</v>
       </c>
       <c r="D465" s="7" t="s">
         <v>32</v>
@@ -23642,7 +23654,7 @@
         <v>1</v>
       </c>
       <c r="H465" s="12" t="s">
-        <v>824</v>
+        <v>1000</v>
       </c>
       <c r="M465" s="9" t="str" cm="1">
         <f t="array" ref="M465">PAGE_NAME(B465)</f>
@@ -23660,19 +23672,16 @@
         <f t="shared" si="20"/>
         <v/>
       </c>
-      <c r="V465" s="12" t="s">
-        <v>700</v>
-      </c>
     </row>
     <row r="466" spans="1:22" ht="102" x14ac:dyDescent="0.2">
       <c r="A466" s="7">
         <v>465</v>
       </c>
       <c r="B466" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C466" s="8" t="s">
-        <v>829</v>
+        <v>992</v>
       </c>
       <c r="D466" s="7" t="s">
         <v>32</v>
@@ -23681,7 +23690,7 @@
         <v>33</v>
       </c>
       <c r="H466" s="12" t="s">
-        <v>830</v>
+        <v>1002</v>
       </c>
       <c r="M466" s="9" t="str" cm="1">
         <f t="array" ref="M466">PAGE_NAME(B466)</f>
@@ -23700,7 +23709,7 @@
         <v/>
       </c>
       <c r="U466" s="12" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
       <c r="V466" s="12" t="s">
         <v>700</v>
@@ -23711,10 +23720,10 @@
         <v>466</v>
       </c>
       <c r="B467" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C467" s="8" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="D467" s="7" t="s">
         <v>36</v>
@@ -23726,7 +23735,7 @@
         <v>1</v>
       </c>
       <c r="H467" s="12" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="O467" s="10" t="str">
         <f t="shared" si="19"/>
@@ -23742,10 +23751,10 @@
         <v>467</v>
       </c>
       <c r="B468" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C468" s="8" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="D468" s="7" t="s">
         <v>36</v>
@@ -23757,7 +23766,7 @@
         <v>1</v>
       </c>
       <c r="H468" s="12" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
       <c r="M468" s="9" t="str" cm="1">
         <f t="array" ref="M468">PAGE_NAME(B468)</f>
@@ -23781,10 +23790,10 @@
         <v>468</v>
       </c>
       <c r="B469" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C469" s="8" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="D469" s="7" t="s">
         <v>40</v>
@@ -23817,10 +23826,10 @@
         <v>469</v>
       </c>
       <c r="B470" s="52" t="s">
+        <v>821</v>
+      </c>
+      <c r="C470" s="8" t="s">
         <v>828</v>
-      </c>
-      <c r="C470" s="8" t="s">
-        <v>837</v>
       </c>
       <c r="D470" s="7" t="s">
         <v>32</v>
@@ -23848,7 +23857,7 @@
         <v/>
       </c>
       <c r="V470" s="12" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="471" spans="1:22" ht="136" x14ac:dyDescent="0.2">
@@ -23856,10 +23865,10 @@
         <v>470</v>
       </c>
       <c r="B471" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C471" s="8" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
       <c r="D471" s="7" t="s">
         <v>36</v>
@@ -23892,10 +23901,10 @@
         <v>471</v>
       </c>
       <c r="B472" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C472" s="8" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="D472" s="7" t="s">
         <v>40</v>
@@ -23907,7 +23916,7 @@
         <v>1</v>
       </c>
       <c r="H472" s="12" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="M472" s="9" t="str" cm="1">
         <f t="array" ref="M472">PAGE_NAME(B472)</f>
@@ -23934,10 +23943,10 @@
         <v>472</v>
       </c>
       <c r="B473" s="52" t="s">
-        <v>828</v>
+        <v>821</v>
       </c>
       <c r="C473" s="8" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="D473" s="7" t="s">
         <v>101</v>
@@ -23970,10 +23979,10 @@
         <v>473</v>
       </c>
       <c r="B474" s="52" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C474" s="8" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="D474" s="7" t="s">
         <v>32</v>
@@ -23985,7 +23994,7 @@
         <v>1</v>
       </c>
       <c r="H474" s="12" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="M474" s="9" t="str" cm="1">
         <f t="array" ref="M474">PAGE_NAME(B474)</f>
@@ -24009,10 +24018,10 @@
         <v>474</v>
       </c>
       <c r="B475" s="52" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C475" s="8" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="D475" s="7" t="s">
         <v>40</v>
@@ -24024,7 +24033,7 @@
         <v>1</v>
       </c>
       <c r="H475" s="12" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
       <c r="M475" s="9" t="str" cm="1">
         <f t="array" ref="M475">PAGE_NAME(B475)</f>
@@ -24048,10 +24057,10 @@
         <v>475</v>
       </c>
       <c r="B476" s="52" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C476" s="8" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="D476" s="7" t="s">
         <v>32</v>
@@ -24063,7 +24072,7 @@
         <v>1</v>
       </c>
       <c r="H476" s="12" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="M476" s="9" t="str" cm="1">
         <f t="array" ref="M476">PAGE_NAME(B476)</f>
@@ -24087,10 +24096,10 @@
         <v>476</v>
       </c>
       <c r="B477" s="52" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C477" s="8" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="D477" s="7" t="s">
         <v>32</v>
@@ -24120,10 +24129,10 @@
         <v>477</v>
       </c>
       <c r="B478" s="52" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
       <c r="C478" s="8" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="D478" s="7" t="s">
         <v>36</v>
@@ -24156,10 +24165,10 @@
         <v>478</v>
       </c>
       <c r="B479" s="52" t="s">
+        <v>834</v>
+      </c>
+      <c r="C479" s="8" t="s">
         <v>843</v>
-      </c>
-      <c r="C479" s="8" t="s">
-        <v>852</v>
       </c>
       <c r="D479" s="7" t="s">
         <v>36</v>
@@ -24192,10 +24201,10 @@
         <v>479</v>
       </c>
       <c r="B480" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C480" s="8" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="D480" s="7" t="s">
         <v>40</v>
@@ -24228,10 +24237,10 @@
         <v>480</v>
       </c>
       <c r="B481" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C481" s="8" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="D481" s="7" t="s">
         <v>36</v>
@@ -24243,7 +24252,7 @@
         <v>1</v>
       </c>
       <c r="H481" s="12" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="M481" s="9" t="str" cm="1">
         <f t="array" ref="M481">PAGE_NAME(B481)</f>
@@ -24267,10 +24276,10 @@
         <v>481</v>
       </c>
       <c r="B482" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C482" s="8" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="D482" s="7" t="s">
         <v>36</v>
@@ -24303,10 +24312,10 @@
         <v>482</v>
       </c>
       <c r="B483" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C483" s="8" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="D483" s="7" t="s">
         <v>32</v>
@@ -24318,7 +24327,7 @@
         <v>1</v>
       </c>
       <c r="H483" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M483" s="9" t="str" cm="1">
         <f t="array" ref="M483">PAGE_NAME(B483)</f>
@@ -24345,10 +24354,10 @@
         <v>483</v>
       </c>
       <c r="B484" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C484" s="8" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="D484" s="7" t="s">
         <v>32</v>
@@ -24360,7 +24369,7 @@
         <v>1</v>
       </c>
       <c r="H484" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M484" s="9" t="str" cm="1">
         <f t="array" ref="M484">PAGE_NAME(B484)</f>
@@ -24387,10 +24396,10 @@
         <v>484</v>
       </c>
       <c r="B485" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C485" s="8" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="D485" s="7" t="s">
         <v>32</v>
@@ -24402,7 +24411,7 @@
         <v>1</v>
       </c>
       <c r="H485" s="12" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="M485" s="9" t="str" cm="1">
         <f t="array" ref="M485">PAGE_NAME(B485)</f>
@@ -24429,10 +24438,10 @@
         <v>485</v>
       </c>
       <c r="B486" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C486" s="8" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="D486" s="7" t="s">
         <v>32</v>
@@ -24444,7 +24453,7 @@
         <v>1</v>
       </c>
       <c r="H486" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M486" s="9" t="str" cm="1">
         <f t="array" ref="M486">PAGE_NAME(B486)</f>
@@ -24471,10 +24480,10 @@
         <v>486</v>
       </c>
       <c r="B487" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C487" s="8" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="D487" s="7" t="s">
         <v>32</v>
@@ -24486,7 +24495,7 @@
         <v>1</v>
       </c>
       <c r="H487" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M487" s="9" t="str" cm="1">
         <f t="array" ref="M487">PAGE_NAME(B487)</f>
@@ -24513,10 +24522,10 @@
         <v>487</v>
       </c>
       <c r="B488" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C488" s="8" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="D488" s="7" t="s">
         <v>32</v>
@@ -24528,7 +24537,7 @@
         <v>1</v>
       </c>
       <c r="H488" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M488" s="9" t="str" cm="1">
         <f t="array" ref="M488">PAGE_NAME(B488)</f>
@@ -24555,10 +24564,10 @@
         <v>488</v>
       </c>
       <c r="B489" s="52" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C489" s="8" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="D489" s="7" t="s">
         <v>36</v>
@@ -24570,7 +24579,7 @@
         <v>1</v>
       </c>
       <c r="H489" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M489" s="9" t="str" cm="1">
         <f t="array" ref="M489">PAGE_NAME(B489)</f>
@@ -24597,10 +24606,10 @@
         <v>489</v>
       </c>
       <c r="B490" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C490" s="8" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="D490" s="7" t="s">
         <v>32</v>
@@ -24633,10 +24642,10 @@
         <v>490</v>
       </c>
       <c r="B491" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C491" s="8" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="D491" s="7" t="s">
         <v>32</v>
@@ -24669,10 +24678,10 @@
         <v>491</v>
       </c>
       <c r="B492" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C492" s="8" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="D492" s="7" t="s">
         <v>32</v>
@@ -24705,10 +24714,10 @@
         <v>492</v>
       </c>
       <c r="B493" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C493" s="8" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="D493" s="7" t="s">
         <v>32</v>
@@ -24741,10 +24750,10 @@
         <v>493</v>
       </c>
       <c r="B494" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C494" s="8" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="D494" s="7" t="s">
         <v>32</v>
@@ -24777,10 +24786,10 @@
         <v>494</v>
       </c>
       <c r="B495" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C495" s="8" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="D495" s="7" t="s">
         <v>32</v>
@@ -24813,10 +24822,10 @@
         <v>495</v>
       </c>
       <c r="B496" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C496" s="8" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="D496" s="7" t="s">
         <v>32</v>
@@ -24849,10 +24858,10 @@
         <v>496</v>
       </c>
       <c r="B497" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C497" s="8" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="D497" s="7" t="s">
         <v>32</v>
@@ -24885,10 +24894,10 @@
         <v>497</v>
       </c>
       <c r="B498" s="52" t="s">
+        <v>859</v>
+      </c>
+      <c r="C498" s="8" t="s">
         <v>868</v>
-      </c>
-      <c r="C498" s="8" t="s">
-        <v>877</v>
       </c>
       <c r="D498" s="7" t="s">
         <v>32</v>
@@ -24921,10 +24930,10 @@
         <v>498</v>
       </c>
       <c r="B499" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C499" s="8" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="D499" s="7" t="s">
         <v>32</v>
@@ -24957,10 +24966,10 @@
         <v>499</v>
       </c>
       <c r="B500" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C500" s="8" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="D500" s="7" t="s">
         <v>32</v>
@@ -24993,10 +25002,10 @@
         <v>500</v>
       </c>
       <c r="B501" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C501" s="8" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="D501" s="7" t="s">
         <v>32</v>
@@ -25029,10 +25038,10 @@
         <v>501</v>
       </c>
       <c r="B502" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C502" s="8" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="D502" s="7" t="s">
         <v>32</v>
@@ -25065,10 +25074,10 @@
         <v>502</v>
       </c>
       <c r="B503" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C503" s="8" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="D503" s="7" t="s">
         <v>32</v>
@@ -25101,10 +25110,10 @@
         <v>503</v>
       </c>
       <c r="B504" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C504" s="8" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="D504" s="7" t="s">
         <v>32</v>
@@ -25137,10 +25146,10 @@
         <v>504</v>
       </c>
       <c r="B505" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C505" s="8" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="D505" s="7" t="s">
         <v>32</v>
@@ -25173,10 +25182,10 @@
         <v>505</v>
       </c>
       <c r="B506" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C506" s="8" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="D506" s="7" t="s">
         <v>32</v>
@@ -25209,10 +25218,10 @@
         <v>506</v>
       </c>
       <c r="B507" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C507" s="8" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="D507" s="7" t="s">
         <v>32</v>
@@ -25245,10 +25254,10 @@
         <v>507</v>
       </c>
       <c r="B508" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C508" s="8" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="D508" s="7" t="s">
         <v>32</v>
@@ -25281,10 +25290,10 @@
         <v>508</v>
       </c>
       <c r="B509" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C509" s="8" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="D509" s="7" t="s">
         <v>32</v>
@@ -25296,7 +25305,7 @@
         <v>1</v>
       </c>
       <c r="H509" s="12" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="M509" s="9" t="str" cm="1">
         <f t="array" ref="M509">PAGE_NAME(B509)</f>
@@ -25320,10 +25329,10 @@
         <v>509</v>
       </c>
       <c r="B510" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C510" s="8" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="D510" s="7" t="s">
         <v>32</v>
@@ -25335,7 +25344,7 @@
         <v>1</v>
       </c>
       <c r="H510" s="12" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="M510" s="9" t="str" cm="1">
         <f t="array" ref="M510">PAGE_NAME(B510)</f>
@@ -25359,10 +25368,10 @@
         <v>510</v>
       </c>
       <c r="B511" s="52" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="C511" s="8" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="D511" s="7" t="s">
         <v>36</v>
@@ -25395,10 +25404,10 @@
         <v>511</v>
       </c>
       <c r="B512" s="52" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="C512" s="8" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="D512" s="7" t="s">
         <v>32</v>
@@ -25410,7 +25419,7 @@
         <v>1</v>
       </c>
       <c r="H512" s="12" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="M512" s="9" t="str" cm="1">
         <f t="array" ref="M512">PAGE_NAME(B512)</f>
@@ -25434,10 +25443,10 @@
         <v>512</v>
       </c>
       <c r="B513" s="52" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="C513" s="8" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="D513" s="7" t="s">
         <v>40</v>
@@ -25449,7 +25458,7 @@
         <v>1</v>
       </c>
       <c r="H513" s="12" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="M513" s="9" t="str" cm="1">
         <f t="array" ref="M513">PAGE_NAME(B513)</f>
@@ -25473,10 +25482,10 @@
         <v>513</v>
       </c>
       <c r="B514" s="52" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="C514" s="8" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="D514" s="7" t="s">
         <v>36</v>
@@ -25509,10 +25518,10 @@
         <v>514</v>
       </c>
       <c r="B515" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C515" s="8" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="D515" s="7" t="s">
         <v>40</v>
@@ -25545,10 +25554,10 @@
         <v>515</v>
       </c>
       <c r="B516" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C516" s="8" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="D516" s="7" t="s">
         <v>36</v>
@@ -25581,10 +25590,10 @@
         <v>516</v>
       </c>
       <c r="B517" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C517" s="8" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="D517" s="7" t="s">
         <v>32</v>
@@ -25596,7 +25605,7 @@
         <v>1</v>
       </c>
       <c r="H517" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M517" s="9" t="str" cm="1">
         <f t="array" ref="M517">PAGE_NAME(B517)</f>
@@ -25623,10 +25632,10 @@
         <v>517</v>
       </c>
       <c r="B518" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C518" s="8" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="D518" s="7" t="s">
         <v>32</v>
@@ -25638,7 +25647,7 @@
         <v>1</v>
       </c>
       <c r="H518" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M518" s="9" t="str" cm="1">
         <f t="array" ref="M518">PAGE_NAME(B518)</f>
@@ -25665,10 +25674,10 @@
         <v>518</v>
       </c>
       <c r="B519" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C519" s="8" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="D519" s="7" t="s">
         <v>32</v>
@@ -25680,7 +25689,7 @@
         <v>1</v>
       </c>
       <c r="H519" s="12" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="M519" s="9" t="str" cm="1">
         <f t="array" ref="M519">PAGE_NAME(B519)</f>
@@ -25707,10 +25716,10 @@
         <v>519</v>
       </c>
       <c r="B520" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C520" s="8" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="D520" s="7" t="s">
         <v>32</v>
@@ -25722,7 +25731,7 @@
         <v>1</v>
       </c>
       <c r="H520" s="12" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="M520" s="9" t="str" cm="1">
         <f t="array" ref="M520">PAGE_NAME(B520)</f>
@@ -25749,10 +25758,10 @@
         <v>520</v>
       </c>
       <c r="B521" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C521" s="8" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D521" s="7" t="s">
         <v>32</v>
@@ -25764,7 +25773,7 @@
         <v>1</v>
       </c>
       <c r="H521" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M521" s="9" t="str" cm="1">
         <f t="array" ref="M521">PAGE_NAME(B521)</f>
@@ -25791,10 +25800,10 @@
         <v>521</v>
       </c>
       <c r="B522" s="52" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C522" s="8" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="D522" s="7" t="s">
         <v>32</v>
@@ -25806,7 +25815,7 @@
         <v>1</v>
       </c>
       <c r="H522" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M522" s="9" t="str" cm="1">
         <f t="array" ref="M522">PAGE_NAME(B522)</f>
@@ -25833,10 +25842,10 @@
         <v>522</v>
       </c>
       <c r="B523" s="52" t="s">
+        <v>890</v>
+      </c>
+      <c r="C523" s="8" t="s">
         <v>899</v>
-      </c>
-      <c r="C523" s="8" t="s">
-        <v>908</v>
       </c>
       <c r="D523" s="7" t="s">
         <v>36</v>
@@ -25848,7 +25857,7 @@
         <v>1</v>
       </c>
       <c r="H523" s="12" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="M523" s="9" t="str" cm="1">
         <f t="array" ref="M523">PAGE_NAME(B523)</f>
@@ -25875,10 +25884,10 @@
         <v>523</v>
       </c>
       <c r="B524" s="52" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="C524" s="8" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="D524" s="7" t="s">
         <v>40</v>
@@ -25911,10 +25920,10 @@
         <v>524</v>
       </c>
       <c r="B525" s="52" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="C525" s="8" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="D525" s="7" t="s">
         <v>32</v>
@@ -25926,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="H525" s="12" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="M525" s="9" t="str" cm="1">
         <f t="array" ref="M525">PAGE_NAME(B525)</f>
@@ -25950,10 +25959,10 @@
         <v>525</v>
       </c>
       <c r="B526" s="52" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="C526" s="8" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="D526" s="7" t="s">
         <v>32</v>
@@ -25986,10 +25995,10 @@
         <v>526</v>
       </c>
       <c r="B527" s="52" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="C527" s="8" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="D527" s="7" t="s">
         <v>40</v>
@@ -26022,10 +26031,10 @@
         <v>527</v>
       </c>
       <c r="B528" s="52" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="C528" s="8" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="D528" s="7" t="s">
         <v>36</v>
@@ -26058,10 +26067,10 @@
         <v>528</v>
       </c>
       <c r="B529" s="52" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="C529" s="8" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="D529" s="7" t="s">
         <v>40</v>
@@ -26094,10 +26103,10 @@
         <v>529</v>
       </c>
       <c r="B530" s="52" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="C530" s="8" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="D530" s="7" t="s">
         <v>40</v>
@@ -26130,10 +26139,10 @@
         <v>530</v>
       </c>
       <c r="B531" s="52" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="C531" s="8" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="D531" s="7" t="s">
         <v>40</v>
@@ -26166,10 +26175,10 @@
         <v>531</v>
       </c>
       <c r="B532" s="52" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="C532" s="8" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="D532" s="7" t="s">
         <v>40</v>
@@ -26202,10 +26211,10 @@
         <v>532</v>
       </c>
       <c r="B533" s="52" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="C533" s="8" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="D533" s="7" t="s">
         <v>36</v>
@@ -26238,10 +26247,10 @@
         <v>533</v>
       </c>
       <c r="B534" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C534" s="8" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="D534" s="7" t="s">
         <v>32</v>
@@ -26274,10 +26283,10 @@
         <v>534</v>
       </c>
       <c r="B535" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C535" s="8" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="D535" s="7" t="s">
         <v>32</v>
@@ -26302,10 +26311,10 @@
         <v>535</v>
       </c>
       <c r="B536" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C536" s="8" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="D536" s="7" t="s">
         <v>32</v>
@@ -26330,10 +26339,10 @@
         <v>536</v>
       </c>
       <c r="B537" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C537" s="8" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="D537" s="7" t="s">
         <v>32</v>
@@ -26358,10 +26367,10 @@
         <v>537</v>
       </c>
       <c r="B538" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C538" s="8" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="D538" s="7" t="s">
         <v>32</v>
@@ -26386,10 +26395,10 @@
         <v>538</v>
       </c>
       <c r="B539" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C539" s="8" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="D539" s="7" t="s">
         <v>32</v>
@@ -26414,10 +26423,10 @@
         <v>539</v>
       </c>
       <c r="B540" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C540" s="8" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="D540" s="7" t="s">
         <v>32</v>
@@ -26442,10 +26451,10 @@
         <v>540</v>
       </c>
       <c r="B541" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C541" s="8" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="D541" s="7" t="s">
         <v>32</v>
@@ -26470,10 +26479,10 @@
         <v>541</v>
       </c>
       <c r="B542" s="52" t="s">
+        <v>915</v>
+      </c>
+      <c r="C542" s="8" t="s">
         <v>924</v>
-      </c>
-      <c r="C542" s="8" t="s">
-        <v>933</v>
       </c>
       <c r="D542" s="7" t="s">
         <v>36</v>
@@ -26498,10 +26507,10 @@
         <v>542</v>
       </c>
       <c r="B543" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C543" s="8" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="D543" s="7" t="s">
         <v>36</v>
@@ -26526,10 +26535,10 @@
         <v>543</v>
       </c>
       <c r="B544" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C544" s="8" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="D544" s="7" t="s">
         <v>32</v>
@@ -26541,7 +26550,7 @@
         <v>1</v>
       </c>
       <c r="H544" s="12" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="M544" s="9" t="str" cm="1">
         <f t="array" ref="M544">PAGE_NAME(B544)</f>
@@ -26557,10 +26566,10 @@
         <v>544</v>
       </c>
       <c r="B545" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C545" s="8" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="D545" s="7" t="s">
         <v>40</v>
@@ -26585,10 +26594,10 @@
         <v>545</v>
       </c>
       <c r="B546" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C546" s="8" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="D546" s="7" t="s">
         <v>40</v>
@@ -26613,10 +26622,10 @@
         <v>546</v>
       </c>
       <c r="B547" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C547" s="8" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="D547" s="7" t="s">
         <v>40</v>
@@ -26641,10 +26650,10 @@
         <v>547</v>
       </c>
       <c r="B548" s="52" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="C548" s="8" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="D548" s="7" t="s">
         <v>40</v>
@@ -26669,10 +26678,10 @@
         <v>548</v>
       </c>
       <c r="B549" s="52" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="C549" s="8" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="D549" s="7" t="s">
         <v>36</v>
@@ -26697,10 +26706,10 @@
         <v>549</v>
       </c>
       <c r="B550" s="52" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="C550" s="8" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="D550" s="7" t="s">
         <v>36</v>
@@ -26712,7 +26721,7 @@
         <v>1</v>
       </c>
       <c r="H550" s="12" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="M550" s="9" t="str" cm="1">
         <f t="array" ref="M550">PAGE_NAME(B550)</f>
@@ -26728,10 +26737,10 @@
         <v>550</v>
       </c>
       <c r="B551" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C551" s="8" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="D551" s="7" t="s">
         <v>32</v>
@@ -26756,10 +26765,10 @@
         <v>551</v>
       </c>
       <c r="B552" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C552" s="8" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="D552" s="7" t="s">
         <v>32</v>
@@ -26784,10 +26793,10 @@
         <v>552</v>
       </c>
       <c r="B553" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C553" s="8" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="D553" s="7" t="s">
         <v>36</v>
@@ -26812,10 +26821,10 @@
         <v>553</v>
       </c>
       <c r="B554" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C554" s="8" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="D554" s="7" t="s">
         <v>36</v>
@@ -26840,10 +26849,10 @@
         <v>554</v>
       </c>
       <c r="B555" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C555" s="8" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="D555" s="7" t="s">
         <v>36</v>
@@ -26868,10 +26877,10 @@
         <v>555</v>
       </c>
       <c r="B556" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C556" s="8" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="D556" s="7" t="s">
         <v>36</v>
@@ -26896,10 +26905,10 @@
         <v>556</v>
       </c>
       <c r="B557" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C557" s="8" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="D557" s="7" t="s">
         <v>36</v>
@@ -26924,10 +26933,10 @@
         <v>557</v>
       </c>
       <c r="B558" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C558" s="8" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="D558" s="7" t="s">
         <v>36</v>
@@ -26952,10 +26961,10 @@
         <v>558</v>
       </c>
       <c r="B559" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C559" s="8" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="D559" s="7" t="s">
         <v>32</v>
@@ -26980,10 +26989,10 @@
         <v>559</v>
       </c>
       <c r="B560" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C560" s="8" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="D560" s="7" t="s">
         <v>32</v>
@@ -27008,10 +27017,10 @@
         <v>560</v>
       </c>
       <c r="B561" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C561" s="8" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="D561" s="7" t="s">
         <v>36</v>
@@ -27036,10 +27045,10 @@
         <v>561</v>
       </c>
       <c r="B562" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C562" s="8" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="D562" s="7" t="s">
         <v>36</v>
@@ -27064,10 +27073,10 @@
         <v>562</v>
       </c>
       <c r="B563" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C563" s="8" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="D563" s="7" t="s">
         <v>32</v>
@@ -27092,10 +27101,10 @@
         <v>563</v>
       </c>
       <c r="B564" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C564" s="8" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="D564" s="7" t="s">
         <v>32</v>
@@ -27120,10 +27129,10 @@
         <v>564</v>
       </c>
       <c r="B565" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C565" s="8" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="D565" s="7" t="s">
         <v>32</v>
@@ -27148,10 +27157,10 @@
         <v>565</v>
       </c>
       <c r="B566" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C566" s="8" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="D566" s="7" t="s">
         <v>32</v>
@@ -27176,10 +27185,10 @@
         <v>566</v>
       </c>
       <c r="B567" s="52" t="s">
+        <v>936</v>
+      </c>
+      <c r="C567" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="C567" s="8" t="s">
-        <v>954</v>
       </c>
       <c r="D567" s="7" t="s">
         <v>36</v>
@@ -27204,10 +27213,10 @@
         <v>567</v>
       </c>
       <c r="B568" s="52" t="s">
+        <v>936</v>
+      </c>
+      <c r="C568" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="C568" s="8" t="s">
-        <v>954</v>
       </c>
       <c r="D568" s="7" t="s">
         <v>36</v>
@@ -27232,10 +27241,10 @@
         <v>568</v>
       </c>
       <c r="B569" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C569" s="8" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="D569" s="7" t="s">
         <v>32</v>
@@ -27260,10 +27269,10 @@
         <v>569</v>
       </c>
       <c r="B570" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C570" s="8" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="D570" s="7" t="s">
         <v>32</v>
@@ -27288,10 +27297,10 @@
         <v>570</v>
       </c>
       <c r="B571" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C571" s="8" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="D571" s="7" t="s">
         <v>32</v>
@@ -27316,10 +27325,10 @@
         <v>571</v>
       </c>
       <c r="B572" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C572" s="8" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="D572" s="7" t="s">
         <v>32</v>
@@ -27344,10 +27353,10 @@
         <v>572</v>
       </c>
       <c r="B573" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C573" s="8" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="D573" s="7" t="s">
         <v>32</v>
@@ -27372,10 +27381,10 @@
         <v>573</v>
       </c>
       <c r="B574" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C574" s="8" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="D574" s="7" t="s">
         <v>32</v>
@@ -27400,10 +27409,10 @@
         <v>574</v>
       </c>
       <c r="B575" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C575" s="8" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="D575" s="7" t="s">
         <v>36</v>
@@ -27428,10 +27437,10 @@
         <v>575</v>
       </c>
       <c r="B576" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C576" s="8" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="D576" s="7" t="s">
         <v>36</v>
@@ -27456,10 +27465,10 @@
         <v>576</v>
       </c>
       <c r="B577" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C577" s="8" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="D577" s="7" t="s">
         <v>36</v>
@@ -27484,10 +27493,10 @@
         <v>577</v>
       </c>
       <c r="B578" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C578" s="8" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="D578" s="7" t="s">
         <v>36</v>
@@ -27512,10 +27521,10 @@
         <v>578</v>
       </c>
       <c r="B579" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C579" s="8" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="D579" s="7" t="s">
         <v>40</v>
@@ -27540,10 +27549,10 @@
         <v>579</v>
       </c>
       <c r="B580" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C580" s="8" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="D580" s="7" t="s">
         <v>40</v>
@@ -27568,10 +27577,10 @@
         <v>580</v>
       </c>
       <c r="B581" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C581" s="8" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="D581" s="7" t="s">
         <v>40</v>
@@ -27596,10 +27605,10 @@
         <v>581</v>
       </c>
       <c r="B582" s="52" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="C582" s="8" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="D582" s="7" t="s">
         <v>40</v>
@@ -27624,10 +27633,10 @@
         <v>582</v>
       </c>
       <c r="B583" s="52" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="C583" s="8" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="D583" s="7" t="s">
         <v>32</v>
@@ -27639,7 +27648,7 @@
         <v>1</v>
       </c>
       <c r="H583" s="12" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="M583" s="9" t="str" cm="1">
         <f t="array" ref="M583">PAGE_NAME(B583)</f>
@@ -27655,10 +27664,10 @@
         <v>583</v>
       </c>
       <c r="B584" s="52" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="C584" s="8" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="D584" s="7" t="s">
         <v>32</v>
@@ -27670,7 +27679,7 @@
         <v>1</v>
       </c>
       <c r="H584" s="12" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="M584" s="9" t="str" cm="1">
         <f t="array" ref="M584">PAGE_NAME(B584)</f>
@@ -27686,10 +27695,10 @@
         <v>584</v>
       </c>
       <c r="B585" s="52" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="C585" s="8" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="D585" s="7" t="s">
         <v>32</v>
@@ -27701,7 +27710,7 @@
         <v>1</v>
       </c>
       <c r="H585" s="12" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="M585" s="9" t="str" cm="1">
         <f t="array" ref="M585">PAGE_NAME(B585)</f>
@@ -27763,7 +27772,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="409.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="59" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B1" s="60"/>
     </row>
@@ -27773,81 +27782,81 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="14" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="B3" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="14" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="14" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="14" t="s">
-        <v>974</v>
+        <v>965</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>975</v>
+        <v>966</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="14" t="s">
-        <v>976</v>
+        <v>967</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>977</v>
+        <v>968</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
-        <v>978</v>
+        <v>969</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
-        <v>979</v>
+        <v>970</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="153" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
-        <v>980</v>
+        <v>971</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
     </row>
   </sheetData>
@@ -27873,19 +27882,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
@@ -27893,13 +27902,13 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="s">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="C2" s="42" t="s">
-        <v>991</v>
+        <v>982</v>
       </c>
       <c r="D2" t="s">
-        <v>992</v>
+        <v>983</v>
       </c>
       <c r="E2" s="43">
         <v>45618</v>
@@ -27920,13 +27929,13 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>993</v>
+        <v>984</v>
       </c>
       <c r="B1" t="s">
         <v>14</v>
       </c>
       <c r="C1" t="s">
-        <v>994</v>
+        <v>985</v>
       </c>
       <c r="D1" t="s">
         <v>16</v>
@@ -27940,7 +27949,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>995</v>
+        <v>986</v>
       </c>
       <c r="D2" t="s">
         <v>52</v>
@@ -27954,7 +27963,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>996</v>
+        <v>987</v>
       </c>
       <c r="D3" t="s">
         <v>51</v>
@@ -27965,7 +27974,7 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>997</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -28002,6 +28011,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EC335ED7BB179244BF94A0DFE64544DC" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d3a0f66abe5d2a0564332877ab55d3f7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eebd8b74-b9de-41b2-9247-c010c4973c2b" xmlns:ns3="b7009bbd-f938-489b-a530-f05273710fff" xmlns:ns4="b5a44311-ed64-4a72-909f-c9dc6973bde2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ec7ca2ee893ff8a0f61d4046c6461645" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="eebd8b74-b9de-41b2-9247-c010c4973c2b"/>
@@ -28255,15 +28273,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19B0E317-5E0E-4728-AB3F-40F2C2B957FB}">
   <ds:schemaRefs>
@@ -28283,6 +28292,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C0B0A19-6928-4F0B-831A-5B9FDDD3F6CE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -28300,12 +28317,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CA84097F-5807-4DCF-92C6-48C9EE26CFB8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>